--- a/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/files/九龙-西南九龙-维港汇 III.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,14 +46,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -65,7 +70,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -76,7 +81,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -87,7 +92,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -97,9 +102,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -147,8 +173,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,19 +221,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,13 +239,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -609,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18536,718 +18574,718 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 III - 1A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>54 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>54 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31&amp;32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31&amp;32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1611呎 (4+房)
-$7,007万
+$7007万
 $43,498/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
-$6,633万
+$6633万
 $47,109/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,088万
+$3088万
 $33,565/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,098万
+$3098万
 $33,348/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,080万
+$3080万
 $33,478/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,078万
+$3078万
 $33,132/呎
 (25年-07月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,150万
+$3150万
 $34,239/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,038万
+$3038万
 $32,702/呎
 (25年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,028万
+$3028万
 $32,913/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,080万
+$3080万
 $33,154/呎
 (24年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,200万
+$3200万
 $34,783/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,072万
+$3072万
 $33,068/呎
 (24年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,988万
+$2988万
 $32,478/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,018万
+$3018万
 $32,487/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,983万
+$2983万
 $32,424/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,998万
+$2998万
 $32,271/呎
 (24年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,978万
+$2978万
 $30,481/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,988万
+$2988万
 $32,164/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,973万
+$2973万
 $32,315/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,008万
+$3008万
 $32,379/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,968万
+$2968万
 $32,261/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,919万
+$2919万
 $31,421/呎
 (25年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,958万
+$2958万
 $32,152/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$3,000万
+$3000万
 $32,293/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$3,000万
+$3000万
 $32,609/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,880万
+$2880万
 $31,001/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,928万
+$2928万
 $29,969/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,938万
+$2938万
 $31,625/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,900万
+$2900万
 $29,683/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,860万
+$2860万
 $30,786/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,880万
+$2880万
 $29,478/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,938万
+$2938万
 $31,625/呎
 (25年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,850万
+$2850万
 $30,978/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,828万
+$2828万
 $30,441/呎
 (24年-07月)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,808万
+$2808万
 $28,741/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,800万
+$2800万
 $30,140/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,788万
+$2788万
 $28,536/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,788万
+$2788万
 $30,011/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,848万
+$2848万
 $30,957/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,788万
+$2788万
 $30,011/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 977呎 (3房)
-$2,750万
+$2750万
 $28,147/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,770万
+$2770万
 $29,817/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,722万
+$2722万
 $29,587/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,760万
+$2760万
 $29,709/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,700万
+$2700万
 $29,348/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,750万
+$2750万
 $29,602/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,665万
+$2665万
 $28,967/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,738万
+$2738万
 $29,473/呎
 (24年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,633万
+$2633万
 $28,620/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,702万
+$2702万
 $29,085/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 920呎 (3房)
-$2,643万
+$2643万
 $28,728/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 929呎 (3房)
-$2,652万
+$2652万
 $28,547/呎
 (25年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 869呎 (3房)
-$2,700万
+$2700万
 $31,070/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 893呎 (3房)
-$2,945万
+$2945万
 $32,982/呎
 (24年-12月)</t>
         </is>
@@ -19255,7 +19293,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -19268,147 +19306,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 III - 1B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>194 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>191 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,290万
+$1290万
 $24,618/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $851万
@@ -19416,7 +19454,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $865万
@@ -19424,7 +19462,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $866万
@@ -19432,7 +19470,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $772万
@@ -19440,7 +19478,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 296呎 (开放式)
 $746万
@@ -19448,23 +19486,23 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,273万
+$1273万
 $24,294/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $834万
@@ -19472,7 +19510,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $848万
@@ -19480,7 +19518,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $849万
@@ -19488,7 +19526,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $935万
@@ -19496,7 +19534,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $687万
@@ -19504,23 +19542,23 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,260万
+$1260万
 $24,046/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $826万
@@ -19528,7 +19566,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $959万
@@ -19536,7 +19574,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $841万
@@ -19544,7 +19582,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $750万
@@ -19552,7 +19590,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $680万
@@ -19560,7 +19598,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $854万
@@ -19569,21 +19607,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,258万
+$1258万
 $24,008/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $822万
@@ -19591,7 +19629,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $915万
@@ -19599,7 +19637,7 @@
 (23年-10月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $837万
@@ -19607,7 +19645,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $778万
@@ -19615,7 +19653,7 @@
 (22年-01月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $676万
@@ -19623,7 +19661,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $850万
@@ -19632,21 +19670,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,255万
+$1255万
 $23,950/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $900万
@@ -19654,7 +19692,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $910万
@@ -19662,7 +19700,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $837万
@@ -19670,7 +19708,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $778万
@@ -19678,7 +19716,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $676万
@@ -19686,7 +19724,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $846万
@@ -19695,21 +19733,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,252万
+$1252万
 $23,893/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $814万
@@ -19717,7 +19755,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $945万
@@ -19725,7 +19763,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $828万
@@ -19733,7 +19771,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $912万
@@ -19741,7 +19779,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $670万
@@ -19749,7 +19787,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $842万
@@ -19758,21 +19796,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,246万
+$1246万
 $23,779/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $810万
@@ -19780,7 +19818,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $890万
@@ -19788,7 +19826,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $824万
@@ -19796,7 +19834,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $907万
@@ -19804,7 +19842,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $666万
@@ -19812,7 +19850,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $838万
@@ -19821,21 +19859,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,242万
+$1242万
 $23,702/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $806万
@@ -19843,7 +19881,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $935万
@@ -19851,7 +19889,7 @@
 (21年-07月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $820万
@@ -19859,7 +19897,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $763万
@@ -19867,7 +19905,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $663万
@@ -19875,7 +19913,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $833万
@@ -19884,21 +19922,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,239万
+$1239万
 $23,651/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $905万
@@ -19906,7 +19944,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $815万
@@ -19914,7 +19952,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $816万
@@ -19922,7 +19960,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $759万
@@ -19930,7 +19968,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $660万
@@ -19938,7 +19976,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $829万
@@ -19947,21 +19985,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,233万
+$1233万
 $23,531/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $798万
@@ -19969,7 +20007,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $926万
@@ -19977,7 +20015,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $812万
@@ -19985,7 +20023,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $755万
@@ -19993,7 +20031,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $657万
@@ -20001,7 +20039,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $903万
@@ -20010,21 +20048,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,222万
+$1222万
 $23,321/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $906万
@@ -20032,7 +20070,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $883万
@@ -20040,7 +20078,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $885万
@@ -20048,7 +20086,7 @@
 (24年-01月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $752万
@@ -20056,7 +20094,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $653万
@@ -20064,7 +20102,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $926万
@@ -20073,21 +20111,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,220万
+$1220万
 $23,282/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $902万
@@ -20095,7 +20133,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $803万
@@ -20103,7 +20141,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $804万
@@ -20111,7 +20149,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $717万
@@ -20119,7 +20157,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $712万
@@ -20127,7 +20165,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $817万
@@ -20136,21 +20174,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,215万
+$1215万
 $23,187/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $786万
@@ -20158,7 +20196,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $912万
@@ -20166,7 +20204,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $876万
@@ -20174,7 +20212,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $744万
@@ -20182,7 +20220,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $739万
@@ -20190,7 +20228,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $890万
@@ -20199,21 +20237,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,208万
+$1208万
 $23,053/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $897万
@@ -20221,7 +20259,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $912万
@@ -20229,7 +20267,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $876万
@@ -20237,7 +20275,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $713万
@@ -20245,7 +20283,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $739万
@@ -20253,7 +20291,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $813万
@@ -20262,21 +20300,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,206万
+$1206万
 $23,015/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $778万
@@ -20284,7 +20322,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $866万
@@ -20292,7 +20330,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $867万
@@ -20300,7 +20338,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $737万
@@ -20308,7 +20346,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $701万
@@ -20316,7 +20354,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $908万
@@ -20325,21 +20363,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,200万
+$1200万
 $22,901/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $884万
@@ -20347,7 +20385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $851万
@@ -20355,7 +20393,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $900万
@@ -20363,7 +20401,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $694万
@@ -20371,7 +20409,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $697万
@@ -20379,7 +20417,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $877万
@@ -20388,21 +20426,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,193万
+$1193万
 $22,764/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $880万
@@ -20410,7 +20448,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $894万
@@ -20418,7 +20456,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $896万
@@ -20426,7 +20464,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $729万
@@ -20434,7 +20472,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $694万
@@ -20442,7 +20480,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $797万
@@ -20451,21 +20489,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,183万
+$1183万
 $22,576/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $839万
@@ -20473,7 +20511,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $879万
@@ -20481,7 +20519,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $854万
@@ -20489,7 +20527,7 @@
 (21年-10月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $717万
@@ -20497,7 +20535,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $720万
@@ -20505,7 +20543,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $905万
@@ -20514,21 +20552,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,173万
+$1173万
 $22,385/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $871万
@@ -20536,7 +20574,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $885万
@@ -20544,7 +20582,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $887万
@@ -20552,7 +20590,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $714万
@@ -20560,7 +20598,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $649万
@@ -20568,7 +20606,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $789万
@@ -20577,21 +20615,21 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,160万
+$1160万
 $22,137/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $759万
@@ -20599,7 +20637,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $881万
@@ -20607,7 +20645,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $846万
@@ -20615,7 +20653,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $689万
@@ -20623,7 +20661,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $713万
@@ -20631,7 +20669,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $859万
@@ -20640,21 +20678,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,150万
+$1150万
 $21,947/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $755万
@@ -20662,7 +20700,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $866万
@@ -20670,7 +20708,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $769万
@@ -20678,7 +20716,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $685万
@@ -20686,7 +20724,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $710万
@@ -20694,7 +20732,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $896万
@@ -20703,21 +20741,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,148万
+$1148万
 $21,908/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $862万
@@ -20725,7 +20763,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $866万
@@ -20733,7 +20771,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $842万
@@ -20741,7 +20779,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $706万
@@ -20749,7 +20787,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $647万
@@ -20757,7 +20795,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $888万
@@ -20766,21 +20804,21 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,284万
+$1284万
 $24,507/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $818万
@@ -20788,7 +20826,7 @@
 (21年-07月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $868万
@@ -20796,7 +20834,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $761万
@@ -20804,7 +20842,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $700万
@@ -20812,7 +20850,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $674万
@@ -20820,7 +20858,7 @@
 (21年-10月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $847万
@@ -20829,21 +20867,21 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,140万
+$1140万
 $21,756/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $849万
@@ -20851,7 +20889,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $853万
@@ -20859,7 +20897,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $844万
@@ -20867,7 +20905,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $675万
@@ -20875,7 +20913,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $670万
@@ -20883,7 +20921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $879万
@@ -20892,21 +20930,21 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,130万
+$1130万
 $21,565/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $848万
@@ -20914,7 +20952,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $862万
@@ -20922,7 +20960,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $863万
@@ -20930,7 +20968,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 278呎 (开放式)
 $703万
@@ -20938,7 +20976,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $669万
@@ -20946,7 +20984,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 331呎 (1房)
 $867万
@@ -20955,21 +20993,21 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,125万
+$1125万
 $21,469/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $846万
@@ -20977,7 +21015,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 $860万
@@ -20985,7 +21023,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 331呎 (1房)
 $826万
@@ -20993,7 +21031,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $702万
@@ -21001,7 +21039,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $668万
@@ -21009,7 +21047,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $839万
@@ -21018,21 +21056,21 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,121万
+$1121万
 $21,401/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 $809万
@@ -21040,7 +21078,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 317呎 (1房)
 $823万
@@ -21048,7 +21086,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 330呎 (1房)
 $850万
@@ -21056,7 +21094,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 277呎 (开放式)
 $700万
@@ -21064,7 +21102,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (开放式)
 $666万
@@ -21072,7 +21110,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 $863万
@@ -21081,21 +21119,21 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-$1,500万
+$1500万
 $30,801/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 294呎 (1房)
 $810万
@@ -21103,7 +21141,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 296呎 (1房)
 $815万
@@ -21111,7 +21149,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 309呎 (1房)
 $838万
@@ -21119,7 +21157,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (开放式)
 $633万
@@ -21127,7 +21165,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 256呎 (开放式)
 $628万
@@ -21135,7 +21173,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 309呎 (1房)
 $853万
@@ -21146,7 +21184,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -21159,135 +21197,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 III - 2座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>140 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>140 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,505万
+$1505万
 $25,765/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $817万
@@ -21295,15 +21333,15 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,293万
+$1293万
 $28,797/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $866万
@@ -21311,30 +21349,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,459万
+$1459万
 $27,785/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,475万
+$1475万
 $25,261/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $876万
@@ -21342,15 +21380,15 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,282万
+$1282万
 $28,559/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $930万
@@ -21358,30 +21396,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,430万
+$1430万
 $27,239/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,461万
+$1461万
 $25,011/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $894万
@@ -21389,15 +21427,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,265万
+$1265万
 $28,174/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $841万
@@ -21405,30 +21443,30 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,416万
+$1416万
 $26,971/呎
 (24年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,410万
+$1410万
 $24,140/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $789万
@@ -21436,15 +21474,15 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,263万
+$1263万
 $28,135/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $837万
@@ -21452,30 +21490,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,409万
+$1409万
 $26,836/呎
 (24年-06月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,453万
+$1453万
 $24,885/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $901万
@@ -21483,15 +21521,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,263万
+$1263万
 $28,135/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $837万
@@ -21499,30 +21537,30 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,409万
+$1409万
 $26,836/呎
 (24年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,439万
+$1439万
 $24,640/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $892万
@@ -21530,15 +21568,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,238万
+$1238万
 $27,572/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $907万
@@ -21546,30 +21584,30 @@
 (24年-01月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,395万
+$1395万
 $26,570/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,389万
+$1389万
 $23,784/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $887万
@@ -21577,15 +21615,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,245万
+$1245万
 $27,718/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $941万
@@ -21593,30 +21631,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,388万
+$1388万
 $26,438/呎
 (24年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,425万
+$1425万
 $24,394/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $883万
@@ -21624,15 +21662,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,230万
+$1230万
 $27,394/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $820万
@@ -21640,30 +21678,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,381万
+$1381万
 $26,307/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,417万
+$1417万
 $24,272/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $878万
@@ -21671,15 +21709,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,232万
+$1232万
 $27,444/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $893万
@@ -21687,30 +21725,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,374万
+$1374万
 $26,176/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,411万
+$1411万
 $24,153/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $874万
@@ -21718,15 +21756,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,225万
+$1225万
 $27,283/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $812万
@@ -21734,30 +21772,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,367万
+$1367万
 $26,045/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,404万
+$1404万
 $24,033/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $823万
@@ -21765,15 +21803,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,220万
+$1220万
 $27,170/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $884万
@@ -21781,30 +21819,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,361万
+$1361万
 $25,917/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,397万
+$1397万
 $23,913/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $855万
@@ -21812,15 +21850,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,214万
+$1214万
 $27,035/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $880万
@@ -21828,30 +21866,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,354万
+$1354万
 $25,787/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,348万
+$1348万
 $23,081/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $851万
@@ -21859,15 +21897,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,260万
+$1260万
 $28,062/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $876万
@@ -21875,30 +21913,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,364万
+$1364万
 $25,976/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,390万
+$1390万
 $23,793/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $851万
@@ -21906,15 +21944,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,208万
+$1208万
 $26,900/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $892万
@@ -21922,30 +21960,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,347万
+$1347万
 $25,659/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,376万
+$1376万
 $23,557/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $822万
@@ -21953,15 +21991,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,248万
+$1248万
 $27,785/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $904万
@@ -21969,30 +22007,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,334万
+$1334万
 $25,405/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,369万
+$1369万
 $23,441/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $838万
@@ -22000,15 +22038,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,190万
+$1190万
 $26,503/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $900万
@@ -22016,30 +22054,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,327万
+$1327万
 $25,278/呎
 (24年-06月)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,362万
+$1362万
 $23,324/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $799万
@@ -22047,15 +22085,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,213万
+$1213万
 $27,022/呎
 (21年-10月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $805万
@@ -22063,30 +22101,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,321万
+$1321万
 $25,153/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,355万
+$1355万
 $23,210/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $830万
@@ -22094,15 +22132,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,229万
+$1229万
 $27,373/呎
 (21年-06月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $801万
@@ -22110,30 +22148,30 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,314万
+$1314万
 $25,027/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,349万
+$1349万
 $23,092/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $791万
@@ -22141,15 +22179,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,172万
+$1172万
 $26,109/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $886万
@@ -22157,30 +22195,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,307万
+$1307万
 $24,903/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,302万
+$1302万
 $22,290/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $787万
@@ -22188,15 +22226,15 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,217万
+$1217万
 $27,100/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $882万
@@ -22204,30 +22242,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,301万
+$1301万
 $24,778/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,335万
+$1335万
 $22,864/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $818万
@@ -22235,15 +22273,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,211万
+$1211万
 $26,967/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $867万
@@ -22251,30 +22289,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,294万
+$1294万
 $24,655/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,295万
+$1295万
 $22,179/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $783万
@@ -22282,15 +22320,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,161万
+$1161万
 $25,849/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $878万
@@ -22298,30 +22336,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,294万
+$1294万
 $24,655/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,282万
+$1282万
 $21,960/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $790万
@@ -22329,15 +22367,15 @@
 (21年-04月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,149万
+$1149万
 $25,595/呎
 (21年-07月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $869万
@@ -22345,30 +22383,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,282万
+$1282万
 $24,413/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,276万
+$1276万
 $21,851/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $806万
@@ -22376,15 +22414,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,143万
+$1143万
 $25,465/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $865万
@@ -22392,30 +22430,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,291万
+$1291万
 $24,590/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,274万
+$1274万
 $21,808/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $804万
@@ -22423,15 +22461,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,169万
+$1169万
 $26,044/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $863万
@@ -22439,30 +22477,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,273万
+$1273万
 $24,243/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,271万
+$1271万
 $21,763/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $759万
@@ -22470,15 +22508,15 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,139万
+$1139万
 $25,364/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $861万
@@ -22486,30 +22524,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,270万
+$1270万
 $24,194/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 584呎 (2房)
-$1,268万
+$1268万
 $21,720/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $777万
@@ -22517,15 +22555,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
-$1,136万
+$1136万
 $25,308/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $860万
@@ -22533,30 +22571,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
-$1,268万
+$1268万
 $24,146/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 547呎 (2房)
-$1,350万
+$1350万
 $24,680/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 291呎 (1房)
 $808万
@@ -22564,15 +22602,15 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 411呎 (2房)
-$1,200万
+$1200万
 $29,197/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $865万
@@ -22580,10 +22618,10 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
-$1,468万
+$1468万
 $30,082/呎
 (24年-07月)</t>
         </is>
